--- a/tame_output/ON/bt/strategyON_20240223.xlsx
+++ b/tame_output/ON/bt/strategyON_20240223.xlsx
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>1.506480126488046</v>
+        <v>1.506276859581771</v>
       </c>
       <c r="E1882" t="n">
-        <v>3.766852474038924</v>
+        <v>3.766771167276414</v>
       </c>
       <c r="F1882" t="n">
         <v>2.401239181360369</v>

--- a/tame_output/ON/bt/strategyON_20240223.xlsx
+++ b/tame_output/ON/bt/strategyON_20240223.xlsx
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309427</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970908</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>1.506276859581771</v>
+        <v>1.506420468104209</v>
       </c>
       <c r="E1882" t="n">
-        <v>3.766771167276414</v>
+        <v>3.766828610685389</v>
       </c>
       <c r="F1882" t="n">
         <v>2.401239181360369</v>

--- a/tame_output/ON/bt/strategyON_20240223.xlsx
+++ b/tame_output/ON/bt/strategyON_20240223.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.2%</t>
+          <t>448.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-13.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.4%</t>
         </is>
       </c>
     </row>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.38653356365031</v>
+        <v>3.386533563650309</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>1.506420468104209</v>
+        <v>1.485429604611893</v>
       </c>
       <c r="E1882" t="n">
-        <v>3.766828610685389</v>
+        <v>3.758432265288463</v>
       </c>
       <c r="F1882" t="n">
         <v>2.401239181360369</v>
